--- a/database/event/5552/event_5552_evp_summary.xlsx
+++ b/database/event/5552/event_5552_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.9826</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
         <v>6.4635</v>
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.227399999999999</v>
+        <v>7.8372</v>
       </c>
       <c r="I2" t="n">
         <v>8.7394</v>
@@ -548,7 +548,7 @@
         <v>3.9826</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E3" t="n">
         <v>6.4635</v>
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8.5091</v>
+        <v>8.166399999999999</v>
       </c>
       <c r="I3" t="n">
         <v>8.9551</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3278</v>
+        <v>5.1448</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2828</v>
+        <v>3.17</v>
       </c>
       <c r="D4" t="n">
-        <v>1.731</v>
+        <v>1.6058</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3278</v>
+        <v>5.1448</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3278</v>
+        <v>5.1448</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.0509</v>
+        <v>5.7639</v>
       </c>
       <c r="I4" t="n">
         <v>6.4274</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0218</v>
+        <v>4.8914</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0942</v>
+        <v>3.0139</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6073</v>
+        <v>1.5048</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0218</v>
+        <v>4.8914</v>
       </c>
       <c r="F5" t="n">
-        <v>5.0218</v>
+        <v>4.8914</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5711</v>
+        <v>5.3667</v>
       </c>
       <c r="I5" t="n">
         <v>5.8359</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8043</v>
+        <v>4.6461</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9602</v>
+        <v>2.8627</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5195</v>
+        <v>1.4071</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8043</v>
+        <v>4.6461</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8043</v>
+        <v>4.6461</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2301</v>
+        <v>4.9821</v>
       </c>
       <c r="I6" t="n">
         <v>5.5556</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6405</v>
+        <v>4.5818</v>
       </c>
       <c r="C7" t="n">
-        <v>2.8593</v>
+        <v>2.8231</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4533</v>
+        <v>1.3815</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6405</v>
+        <v>4.5818</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6405</v>
+        <v>4.5818</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9733</v>
+        <v>4.8812</v>
       </c>
       <c r="I7" t="n">
         <v>5.0901</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3273</v>
+        <v>4.2639</v>
       </c>
       <c r="C8" t="n">
-        <v>2.6663</v>
+        <v>2.6273</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3268</v>
+        <v>1.2548</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3273</v>
+        <v>4.2639</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3273</v>
+        <v>4.2639</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4822</v>
+        <v>4.3828</v>
       </c>
       <c r="I8" t="n">
         <v>4.6088</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.0691</v>
+        <v>4.0168</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5072</v>
+        <v>2.475</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2225</v>
+        <v>1.1564</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0691</v>
+        <v>4.0168</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0691</v>
+        <v>4.0168</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0773</v>
+        <v>4.0168</v>
       </c>
       <c r="I9" t="n">
         <v>4.1537</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7259</v>
+        <v>3.5818</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2958</v>
+        <v>2.207</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0838</v>
+        <v>0.9831</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7259</v>
+        <v>3.5818</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7259</v>
+        <v>3.5818</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7259</v>
+        <v>3.5818</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9577</v>
+        <v>3.7351</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>445</v>
+        <v>330</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9577</v>
+        <v>3.7351</v>
       </c>
       <c r="N10" t="n">
-        <v>445</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6516</v>
+        <v>3.5491</v>
       </c>
       <c r="C11" t="n">
-        <v>2.25</v>
+        <v>2.1868</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0538</v>
+        <v>0.9701</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6516</v>
+        <v>3.5491</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6516</v>
+        <v>3.5491</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6516</v>
+        <v>3.5491</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8252</v>
+        <v>3.9577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8252</v>
+        <v>3.9577</v>
       </c>
       <c r="N11" t="n">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6494</v>
+        <v>3.5177</v>
       </c>
       <c r="C12" t="n">
-        <v>2.2486</v>
+        <v>2.1675</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0529</v>
+        <v>0.9575</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6494</v>
+        <v>3.5177</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6494</v>
+        <v>3.5177</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6494</v>
+        <v>3.5177</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7351</v>
+        <v>3.8252</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>330</v>
+        <v>454</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7351</v>
+        <v>3.8252</v>
       </c>
       <c r="N12" t="n">
-        <v>330</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13">
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4942</v>
+        <v>3.4167</v>
       </c>
       <c r="C13" t="n">
-        <v>2.153</v>
+        <v>2.1052</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9902</v>
+        <v>0.9173</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4942</v>
+        <v>3.4167</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4942</v>
+        <v>3.4167</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4942</v>
+        <v>3.4167</v>
       </c>
       <c r="I13" t="n">
         <v>3.5929</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4174</v>
+        <v>3.3416</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1057</v>
+        <v>2.059</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.8874</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4174</v>
+        <v>3.3416</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4174</v>
+        <v>3.3416</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4174</v>
+        <v>3.3416</v>
       </c>
       <c r="I14" t="n">
         <v>3.5139</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1777</v>
+        <v>3.1082</v>
       </c>
       <c r="C15" t="n">
-        <v>1.958</v>
+        <v>1.9152</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.7944</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1777</v>
+        <v>3.1082</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1777</v>
+        <v>3.1082</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1777</v>
+        <v>3.1082</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2675</v>
+        <v>3.2412</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2675</v>
+        <v>3.2412</v>
       </c>
       <c r="N15" t="n">
-        <v>283</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1668</v>
+        <v>3.1072</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9513</v>
+        <v>1.9145</v>
       </c>
       <c r="D16" t="n">
-        <v>0.858</v>
+        <v>0.794</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1668</v>
+        <v>3.1072</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1668</v>
+        <v>3.1072</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1668</v>
+        <v>3.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2412</v>
+        <v>3.2675</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2412</v>
+        <v>3.2675</v>
       </c>
       <c r="N16" t="n">
-        <v>248</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.1519</v>
+        <v>3.0936</v>
       </c>
       <c r="C17" t="n">
-        <v>1.9421</v>
+        <v>1.9062</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8519</v>
+        <v>0.7886</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1519</v>
+        <v>3.0936</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1519</v>
+        <v>3.0936</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1519</v>
+        <v>3.0936</v>
       </c>
       <c r="I17" t="n">
         <v>3.226</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0756</v>
+        <v>3.03</v>
       </c>
       <c r="C18" t="n">
-        <v>1.8951</v>
+        <v>1.867</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.7632</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0756</v>
+        <v>3.03</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0756</v>
+        <v>3.03</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0756</v>
+        <v>3.03</v>
       </c>
       <c r="I18" t="n">
         <v>3.1333</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5142</v>
+        <v>2.4676</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5492</v>
+        <v>1.5204</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5392</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5142</v>
+        <v>2.4676</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5142</v>
+        <v>2.4676</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5142</v>
+        <v>2.4676</v>
       </c>
       <c r="I19" t="n">
         <v>2.5732</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5222</v>
+        <v>1.4884</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5766</v>
+        <v>0.5185</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4704</v>
+        <v>2.4156</v>
       </c>
       <c r="I20" t="n">
         <v>2.5402</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.3622</v>
+        <v>2.3098</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4555</v>
+        <v>1.4232</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5329</v>
+        <v>0.4763</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3622</v>
+        <v>2.3098</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3622</v>
+        <v>2.3098</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3622</v>
+        <v>2.3098</v>
       </c>
       <c r="I21" t="n">
         <v>2.4289</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0879</v>
+        <v>2.0416</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2865</v>
+        <v>1.258</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4221</v>
+        <v>0.3695</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0879</v>
+        <v>2.0416</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0879</v>
+        <v>2.0416</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0879</v>
+        <v>2.0416</v>
       </c>
       <c r="I22" t="n">
         <v>2.1469</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0337</v>
+        <v>1.9961</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2531</v>
+        <v>1.2299</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4002</v>
+        <v>0.3513</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0337</v>
+        <v>1.9961</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0337</v>
+        <v>1.9961</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0337</v>
+        <v>1.9961</v>
       </c>
       <c r="I23" t="n">
         <v>2.0815</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9927</v>
+        <v>1.9485</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2278</v>
+        <v>1.2006</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3836</v>
+        <v>0.3324</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9927</v>
+        <v>1.9485</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9927</v>
+        <v>1.9485</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9927</v>
+        <v>1.9485</v>
       </c>
       <c r="I24" t="n">
         <v>2.049</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8221</v>
+        <v>1.8018</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1227</v>
+        <v>1.1102</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3147</v>
+        <v>0.2739</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8221</v>
+        <v>1.8018</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8221</v>
+        <v>1.8018</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8221</v>
+        <v>1.8018</v>
       </c>
       <c r="I25" t="n">
         <v>1.8477</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6812</v>
+        <v>1.6563</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0359</v>
+        <v>1.0205</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2578</v>
+        <v>0.216</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6812</v>
+        <v>1.6563</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6812</v>
+        <v>1.6563</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6812</v>
+        <v>1.6563</v>
       </c>
       <c r="I26" t="n">
         <v>1.7127</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6226</v>
+        <v>1.6045</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9998</v>
+        <v>0.9886</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2341</v>
+        <v>0.1953</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6226</v>
+        <v>1.6045</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6226</v>
+        <v>1.6045</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6226</v>
+        <v>1.6045</v>
       </c>
       <c r="I27" t="n">
         <v>1.6454</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.4414</v>
+        <v>1.4094</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8881</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1609</v>
+        <v>0.1176</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4414</v>
+        <v>1.4094</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4414</v>
+        <v>1.4094</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.4414</v>
+        <v>1.4094</v>
       </c>
       <c r="I28" t="n">
         <v>1.4821</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1196</v>
+        <v>1.1113</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6899</v>
+        <v>0.6847</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0309</v>
+        <v>-0.0012</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1196</v>
+        <v>1.1113</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1196</v>
+        <v>1.1113</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1196</v>
+        <v>1.1113</v>
       </c>
       <c r="I29" t="n">
         <v>1.1301</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1193</v>
+        <v>1.0945</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6897</v>
+        <v>0.6744</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0308</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1193</v>
+        <v>1.0945</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1193</v>
+        <v>1.0945</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1193</v>
+        <v>1.0945</v>
       </c>
       <c r="I30" t="n">
         <v>1.1509</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1035</v>
+        <v>1.0912</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6724</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0244</v>
+        <v>-0.0092</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1035</v>
+        <v>1.0912</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1035</v>
+        <v>1.0912</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1035</v>
+        <v>1.0912</v>
       </c>
       <c r="I31" t="n">
         <v>1.119</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.058</v>
+        <v>1.0462</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6519</v>
+        <v>0.6446</v>
       </c>
       <c r="D32" t="n">
-        <v>0.006</v>
+        <v>-0.0271</v>
       </c>
       <c r="E32" t="n">
-        <v>1.058</v>
+        <v>1.0462</v>
       </c>
       <c r="F32" t="n">
-        <v>1.058</v>
+        <v>1.0462</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.058</v>
+        <v>1.0462</v>
       </c>
       <c r="I32" t="n">
         <v>1.0728</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.99</v>
+        <v>0.9717</v>
       </c>
       <c r="C33" t="n">
-        <v>0.61</v>
+        <v>0.5987</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0214</v>
+        <v>-0.0568</v>
       </c>
       <c r="E33" t="n">
-        <v>0.99</v>
+        <v>0.9717</v>
       </c>
       <c r="F33" t="n">
-        <v>0.99</v>
+        <v>0.9717</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.99</v>
+        <v>0.9717</v>
       </c>
       <c r="I33" t="n">
         <v>1.0133</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9549</v>
+        <v>0.9407</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5884</v>
+        <v>0.5796</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0356</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9549</v>
+        <v>0.9407</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9549</v>
+        <v>0.9407</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9549</v>
+        <v>0.9407</v>
       </c>
       <c r="I34" t="n">
         <v>0.9728</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9445</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>0.582</v>
+        <v>0.5544</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0398</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9445</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9445</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9445</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>1.0033</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8489</v>
+        <v>0.8363</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5231</v>
+        <v>0.5153</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0784</v>
+        <v>-0.1107</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8489</v>
+        <v>0.8363</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8489</v>
+        <v>0.8363</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8489</v>
+        <v>0.8363</v>
       </c>
       <c r="I36" t="n">
         <v>0.8648</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7693</v>
+        <v>0.7664</v>
       </c>
       <c r="C37" t="n">
-        <v>0.474</v>
+        <v>0.4722</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1106</v>
+        <v>-0.1386</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7693</v>
+        <v>0.7664</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7693</v>
+        <v>0.7664</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7693</v>
+        <v>0.7664</v>
       </c>
       <c r="I37" t="n">
         <v>0.7729</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6755</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4162</v>
+        <v>0.4146</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1485</v>
+        <v>-0.1758</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6755</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6755</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6755</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>0.6786</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5957</v>
+        <v>0.576</v>
       </c>
       <c r="C39" t="n">
-        <v>0.367</v>
+        <v>0.3549</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1807</v>
+        <v>-0.2144</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5957</v>
+        <v>0.576</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5957</v>
+        <v>0.576</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5957</v>
+        <v>0.576</v>
       </c>
       <c r="I39" t="n">
         <v>0.6211</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5291</v>
+        <v>0.5246</v>
       </c>
       <c r="C40" t="n">
-        <v>0.326</v>
+        <v>0.3232</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2076</v>
+        <v>-0.2349</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5291</v>
+        <v>0.5246</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5291</v>
+        <v>0.5246</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5291</v>
+        <v>0.5246</v>
       </c>
       <c r="I40" t="n">
-        <v>0.544</v>
+        <v>0.5246</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>267</v>
+        <v>112</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.544</v>
+        <v>0.5246</v>
       </c>
       <c r="N40" t="n">
-        <v>267</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5246</v>
+        <v>0.5173</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3232</v>
+        <v>0.3187</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2094</v>
+        <v>-0.2378</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5246</v>
+        <v>0.5173</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5246</v>
+        <v>0.5173</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5246</v>
+        <v>0.5173</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5246</v>
+        <v>0.544</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>112</v>
+        <v>267</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5246</v>
+        <v>0.544</v>
       </c>
       <c r="N41" t="n">
-        <v>112</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42">
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4875</v>
+        <v>0.4821</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3004</v>
+        <v>0.2971</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2244</v>
+        <v>-0.2518</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4875</v>
+        <v>0.4821</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4875</v>
+        <v>0.4821</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4875</v>
+        <v>0.4821</v>
       </c>
       <c r="I42" t="n">
         <v>0.4944</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3992</v>
+        <v>0.3962</v>
       </c>
       <c r="C43" t="n">
-        <v>0.246</v>
+        <v>0.2441</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2601</v>
+        <v>-0.2861</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3992</v>
+        <v>0.3962</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3992</v>
+        <v>0.3962</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3992</v>
+        <v>0.3962</v>
       </c>
       <c r="I43" t="n">
         <v>0.4029</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2677</v>
+        <v>0.2618</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1649</v>
+        <v>0.1613</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3132</v>
+        <v>-0.3396</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2677</v>
+        <v>0.2618</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2677</v>
+        <v>0.2618</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2677</v>
+        <v>0.2618</v>
       </c>
       <c r="I44" t="n">
         <v>0.2753</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1889</v>
+        <v>0.1868</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1164</v>
+        <v>0.1151</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3451</v>
+        <v>-0.3695</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1889</v>
+        <v>0.1868</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1889</v>
+        <v>0.1868</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1889</v>
+        <v>0.1868</v>
       </c>
       <c r="I45" t="n">
         <v>0.1916</v>
@@ -2526,7 +2526,7 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3786</v>
+        <v>-0.4018</v>
       </c>
       <c r="E46" t="n">
         <v>0.1058</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0247</v>
+        <v>0.0244</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0152</v>
+        <v>0.015</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4114</v>
+        <v>-0.4342</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0247</v>
+        <v>0.0244</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0247</v>
+        <v>0.0244</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0247</v>
+        <v>0.0244</v>
       </c>
       <c r="I47" t="n">
         <v>0.025</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0067</v>
+        <v>-0.0066</v>
       </c>
       <c r="C48" t="n">
         <v>-0.0041</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4241</v>
+        <v>-0.4465</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0067</v>
+        <v>-0.0066</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0067</v>
+        <v>-0.0066</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0067</v>
+        <v>-0.0066</v>
       </c>
       <c r="I48" t="n">
         <v>-0.0068</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0476</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4525</v>
+        <v>-0.4747</v>
       </c>
       <c r="E49" t="n">
         <v>-0.0772</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1007</v>
+        <v>-0.1004</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.062</v>
+        <v>-0.0619</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.462</v>
+        <v>-0.4839</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1007</v>
+        <v>-0.1004</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1007</v>
+        <v>-0.1004</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1007</v>
+        <v>-0.1004</v>
       </c>
       <c r="I50" t="n">
         <v>-0.1012</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0922</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4818</v>
+        <v>-0.5036</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1497</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1518</v>
+        <v>-0.1501</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0935</v>
+        <v>-0.0925</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4827</v>
+        <v>-0.5037</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1518</v>
+        <v>-0.1501</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1518</v>
+        <v>-0.1501</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1518</v>
+        <v>-0.1501</v>
       </c>
       <c r="I52" t="n">
         <v>-0.1539</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1628</v>
+        <v>-0.161</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1003</v>
+        <v>-0.0992</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4871</v>
+        <v>-0.5081</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1628</v>
+        <v>-0.161</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1628</v>
+        <v>-0.161</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1628</v>
+        <v>-0.161</v>
       </c>
       <c r="I53" t="n">
         <v>-0.1651</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1849</v>
+        <v>-0.1808</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1139</v>
+        <v>-0.1114</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4961</v>
+        <v>-0.5159</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1849</v>
+        <v>-0.1808</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1849</v>
+        <v>-0.1808</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1849</v>
+        <v>-0.1808</v>
       </c>
       <c r="I54" t="n">
         <v>-0.1901</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2942</v>
+        <v>-0.292</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1813</v>
+        <v>-0.1799</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5402</v>
+        <v>-0.5602</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2942</v>
+        <v>-0.292</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2942</v>
+        <v>-0.292</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2942</v>
+        <v>-0.292</v>
       </c>
       <c r="I55" t="n">
         <v>-0.2969</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1831</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5414</v>
+        <v>-0.5623</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2972</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2285</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5712</v>
+        <v>-0.5917</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3709</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4626</v>
+        <v>-0.4541</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.285</v>
+        <v>-0.2798</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6082</v>
+        <v>-0.6248</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4626</v>
+        <v>-0.4541</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4626</v>
+        <v>-0.4541</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4626</v>
+        <v>-0.4541</v>
       </c>
       <c r="I58" t="n">
         <v>-0.4735</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2937</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6139</v>
+        <v>-0.6338</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4766</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3208</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6317</v>
+        <v>-0.6513</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5206</v>
@@ -3216,7 +3216,7 @@
         <v>-0.4072</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6883</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6608000000000001</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7272</v>
+        <v>-0.7191</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4481</v>
+        <v>-0.4431</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7151</v>
+        <v>-0.7304</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7272</v>
+        <v>-0.7191</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7272</v>
+        <v>-0.7191</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7272</v>
+        <v>-0.7191</v>
       </c>
       <c r="I62" t="n">
         <v>-0.7374000000000001</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.731</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4504</v>
+        <v>-0.4488</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7167</v>
+        <v>-0.7341</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.731</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.731</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.731</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>-0.7344000000000001</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5805</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.802</v>
+        <v>-0.8193</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9422</v>
@@ -3390,93 +3390,93 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1094</v>
+        <v>-1.1062</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.6836</v>
+        <v>-0.6816</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.1094</v>
+        <v>-1.1062</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.1094</v>
+        <v>-1.1062</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.1094</v>
+        <v>-1.1062</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.1094</v>
+        <v>-1.1249</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-1.1094</v>
+        <v>-1.1249</v>
       </c>
       <c r="N65" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1145</v>
+        <v>-1.1094</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.6867</v>
+        <v>-0.6836</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8716</v>
+        <v>-0.8859</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.1145</v>
+        <v>-1.1094</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.1145</v>
+        <v>-1.1094</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.1145</v>
+        <v>-1.1094</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.1249</v>
+        <v>-1.1094</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.1249</v>
+        <v>-1.1094</v>
       </c>
       <c r="N66" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67">
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1946</v>
+        <v>-1.1681</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.7361</v>
+        <v>-0.7197</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.904</v>
+        <v>-0.9093</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.1946</v>
+        <v>-1.1681</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.1946</v>
+        <v>-1.1681</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.1946</v>
+        <v>-1.1681</v>
       </c>
       <c r="I67" t="n">
         <v>-1.2283</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2098</v>
+        <v>-1.1874</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.7454</v>
+        <v>-0.7316</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9101</v>
+        <v>-0.917</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2098</v>
+        <v>-1.1874</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.2098</v>
+        <v>-1.1874</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.2098</v>
+        <v>-1.1874</v>
       </c>
       <c r="I68" t="n">
         <v>-1.2382</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7749</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9294</v>
+        <v>-0.9449</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2576</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8097</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9522</v>
+        <v>-0.9674</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3141</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8168</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9569</v>
+        <v>-0.9721</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3257</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.4758</v>
+        <v>-1.4593</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.9093</v>
+        <v>-0.8992</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0176</v>
+        <v>-1.0253</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.4758</v>
+        <v>-1.4593</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.4758</v>
+        <v>-1.4593</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.4758</v>
+        <v>-1.4593</v>
       </c>
       <c r="I72" t="n">
         <v>-1.4965</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5031</v>
+        <v>-1.4864</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.9262</v>
+        <v>-0.9159</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0286</v>
+        <v>-1.0361</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5031</v>
+        <v>-1.4864</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.5031</v>
+        <v>-1.4864</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.5031</v>
+        <v>-1.4864</v>
       </c>
       <c r="I73" t="n">
         <v>-1.5242</v>
@@ -3814,7 +3814,7 @@
         <v>-0.9305</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0314</v>
+        <v>-1.0455</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5101</v>
@@ -3860,7 +3860,7 @@
         <v>-1.078</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1282</v>
+        <v>-1.141</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7496</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.8369</v>
+        <v>-1.8164</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.1318</v>
+        <v>-1.1192</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1634</v>
+        <v>-1.1676</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.8369</v>
+        <v>-1.8164</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8369</v>
+        <v>-1.8164</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.8369</v>
+        <v>-1.8164</v>
       </c>
       <c r="I76" t="n">
         <v>-1.8627</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9296</v>
+        <v>-1.8939</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.1889</v>
+        <v>-1.1669</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2009</v>
+        <v>-1.1984</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9296</v>
+        <v>-1.8939</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.9296</v>
+        <v>-1.8939</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.9296</v>
+        <v>-1.8939</v>
       </c>
       <c r="I77" t="n">
         <v>-1.9749</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.9351</v>
+        <v>-1.9207</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1923</v>
+        <v>-1.1835</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2031</v>
+        <v>-1.2091</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.9351</v>
+        <v>-1.9207</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.9351</v>
+        <v>-1.9207</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.9351</v>
+        <v>-1.9207</v>
       </c>
       <c r="I78" t="n">
         <v>-1.9532</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.5786</v>
+        <v>-2.5594</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.5888</v>
+        <v>-1.577</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4631</v>
+        <v>-1.4636</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.5786</v>
+        <v>-2.5594</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.5786</v>
+        <v>-2.5594</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.5786</v>
+        <v>-2.5594</v>
       </c>
       <c r="I79" t="n">
         <v>-2.6027</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.6977</v>
+        <v>-2.6577</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6622</v>
+        <v>-1.6376</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5112</v>
+        <v>-1.5027</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.6977</v>
+        <v>-2.6577</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.6977</v>
+        <v>-2.6577</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.6977</v>
+        <v>-2.6577</v>
       </c>
       <c r="I80" t="n">
         <v>-2.7483</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.031</v>
+        <v>-3.0084</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.8676</v>
+        <v>-1.8537</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6458</v>
+        <v>-1.6425</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.031</v>
+        <v>-3.0084</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.031</v>
+        <v>-3.0084</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.031</v>
+        <v>-3.0084</v>
       </c>
       <c r="I81" t="n">
         <v>-3.0593</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.4461</v>
+        <v>-3.4205</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.1234</v>
+        <v>-2.1076</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.8135</v>
+        <v>-1.8066</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.4461</v>
+        <v>-3.4205</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.4461</v>
+        <v>-3.4205</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.4461</v>
+        <v>-3.4205</v>
       </c>
       <c r="I82" t="n">
         <v>-3.4783</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-5.0904</v>
+        <v>-4.922</v>
       </c>
       <c r="C83" t="n">
-        <v>-3.1365</v>
+        <v>-3.0327</v>
       </c>
       <c r="D83" t="n">
-        <v>-2.4778</v>
+        <v>-2.4048</v>
       </c>
       <c r="E83" t="n">
-        <v>-5.0904</v>
+        <v>-4.922</v>
       </c>
       <c r="F83" t="n">
-        <v>-5.0904</v>
+        <v>-4.922</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-5.0904</v>
+        <v>-4.922</v>
       </c>
       <c r="I83" t="n">
         <v>-5.3076</v>
